--- a/frontend/demo/sample/S2_sample_dataset.xlsx
+++ b/frontend/demo/sample/S2_sample_dataset.xlsx
@@ -509,7 +509,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Headroom Monitor · illustrative dataset (scenario S2)</t>
+          <t>Headroom Monitor · illustrative dataset (scenario S2 · Large customer slows down)</t>
         </is>
       </c>
     </row>
